--- a/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
+++ b/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T19:07:24+00:00</t>
+    <t>2026-04-28T19:22:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
+++ b/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T19:22:30+00:00</t>
+    <t>2026-04-29T06:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
+++ b/feat/ig-publisher-migration/ValueSet-mii-vs-pro-eortc-qlq-c30-scale-7pt.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T06:19:54+00:00</t>
+    <t>2026-04-29T08:45:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
